--- a/ages_skos.xlsx
+++ b/ages_skos.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uppsalauniversitet-my.sharepoint.com/personal/daniel_lowenborg_arkeologi_uu_se/Documents/Swedigarch M3/Projekt/Samlingar och samband/Vokabulär/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\ks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5E5B3F24-0995-40B2-B2C1-24AF82CD3514}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C971D960-CF5F-442D-867D-9C23EBA0E6B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2955" yWindow="2055" windowWidth="21600" windowHeight="12645" tabRatio="766" activeTab="2" xr2:uid="{B311A485-C470-444A-A92B-1ECDED2E4894}"/>
+    <workbookView xWindow="5910" yWindow="315" windowWidth="21600" windowHeight="14040" tabRatio="766" activeTab="1" xr2:uid="{B311A485-C470-444A-A92B-1ECDED2E4894}"/>
   </bookViews>
   <sheets>
     <sheet name="Ark_objekt_anläggning" sheetId="9" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="880" uniqueCount="493">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="882" uniqueCount="493">
   <si>
     <t>nedgrävning</t>
   </si>
@@ -897,9 +897,6 @@
     <t>slana</t>
   </si>
   <si>
-    <t>gravkantränna</t>
-  </si>
-  <si>
     <t>gravkor</t>
   </si>
   <si>
@@ -1522,13 +1519,16 @@
   </si>
   <si>
     <t>stolpmärke</t>
+  </si>
+  <si>
+    <t>klumpstensgrav</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1548,6 +1548,14 @@
       <b/>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1589,7 +1597,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1611,9 +1619,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Hyperlänk" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="68">
@@ -2881,10 +2890,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{056C5752-C461-49AB-85F6-0277088EA35B}" name="Table12" displayName="Table12" ref="A1:M163" totalsRowShown="0">
-  <autoFilter ref="A1:M163" xr:uid="{056C5752-C461-49AB-85F6-0277088EA35B}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M162">
-    <sortCondition ref="C1:C162"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{056C5752-C461-49AB-85F6-0277088EA35B}" name="Table12" displayName="Table12" ref="A1:M164" totalsRowShown="0">
+  <autoFilter ref="A1:M164" xr:uid="{056C5752-C461-49AB-85F6-0277088EA35B}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M163">
+    <sortCondition ref="C1:C163"/>
   </sortState>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{9D3424A3-D8B0-4710-B559-CE896FE1F562}" name="Kod"/>
@@ -3036,7 +3045,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office-tema">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -3332,7 +3341,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3059113B-3759-497F-962C-BD9787861F75}">
-  <dimension ref="A1:X163"/>
+  <dimension ref="A1:X164"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.42578125" customWidth="1"/>
@@ -3352,62 +3361,62 @@
   <sheetData>
     <row r="1" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C1" t="s">
         <v>257</v>
       </c>
       <c r="D1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="E1" t="s">
+        <v>443</v>
+      </c>
+      <c r="F1" t="s">
         <v>444</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>445</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>446</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
+        <v>461</v>
+      </c>
+      <c r="J1" t="s">
+        <v>450</v>
+      </c>
+      <c r="K1" t="s">
         <v>447</v>
       </c>
-      <c r="I1" t="s">
-        <v>462</v>
-      </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
+        <v>448</v>
+      </c>
+      <c r="M1" t="s">
         <v>451</v>
-      </c>
-      <c r="K1" t="s">
-        <v>448</v>
-      </c>
-      <c r="L1" t="s">
-        <v>449</v>
-      </c>
-      <c r="M1" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B2" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="E2" s="14" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B3" t="s">
         <v>108</v>
@@ -3416,24 +3425,24 @@
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="E3" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="F3" t="s">
         <v>111</v>
       </c>
       <c r="G3" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="M3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B4" t="s">
         <v>172</v>
@@ -3447,7 +3456,7 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C5">
         <v>2</v>
@@ -3458,7 +3467,7 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C6">
         <v>2</v>
@@ -3469,7 +3478,7 @@
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B7" t="s">
         <v>126</v>
@@ -3486,7 +3495,7 @@
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B8" t="s">
         <v>86</v>
@@ -3498,7 +3507,7 @@
         <v>108</v>
       </c>
       <c r="H8" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="I8" t="s">
         <v>93</v>
@@ -3506,7 +3515,7 @@
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C9">
         <v>2</v>
@@ -3515,18 +3524,18 @@
         <v>108</v>
       </c>
       <c r="E9" t="s">
+        <v>431</v>
+      </c>
+      <c r="F9" t="s">
         <v>432</v>
       </c>
-      <c r="F9" t="s">
-        <v>433</v>
-      </c>
       <c r="H9" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B10" t="s">
         <v>140</v>
@@ -3538,15 +3547,15 @@
         <v>108</v>
       </c>
       <c r="H10" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B11" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C11">
         <v>2</v>
@@ -3555,12 +3564,12 @@
         <v>108</v>
       </c>
       <c r="H11" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B12" t="s">
         <v>43</v>
@@ -3625,10 +3634,10 @@
         <v>108</v>
       </c>
       <c r="H16" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="I16" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
@@ -3645,10 +3654,10 @@
         <v>50</v>
       </c>
       <c r="H17" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="I17" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
@@ -3662,15 +3671,15 @@
         <v>108</v>
       </c>
       <c r="H18" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="I18" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C19">
         <v>2</v>
@@ -3712,7 +3721,7 @@
         <v>108</v>
       </c>
       <c r="H22" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
@@ -3748,7 +3757,7 @@
         <v>108</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
@@ -3762,10 +3771,10 @@
         <v>108</v>
       </c>
       <c r="H26" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="I26" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
@@ -3817,10 +3826,10 @@
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B31" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C31">
         <v>2</v>
@@ -3831,10 +3840,10 @@
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B32" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C32">
         <v>2</v>
@@ -3854,7 +3863,7 @@
         <v>108</v>
       </c>
       <c r="G33" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="34" spans="2:9" x14ac:dyDescent="0.25">
@@ -3901,7 +3910,7 @@
         <v>108</v>
       </c>
       <c r="G37" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="38" spans="2:9" x14ac:dyDescent="0.25">
@@ -3915,7 +3924,7 @@
         <v>108</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="39" spans="2:9" x14ac:dyDescent="0.25">
@@ -3943,7 +3952,7 @@
         <v>48</v>
       </c>
       <c r="G40" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H40" t="s">
         <v>99</v>
@@ -3965,7 +3974,7 @@
     </row>
     <row r="42" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C42">
         <v>2</v>
@@ -4034,7 +4043,7 @@
     </row>
     <row r="48" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C48">
         <v>2</v>
@@ -4079,7 +4088,7 @@
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C51">
         <v>2</v>
@@ -4116,7 +4125,7 @@
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C53">
         <v>2</v>
@@ -4139,7 +4148,7 @@
         <v>118</v>
       </c>
       <c r="I54" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="K54" t="s">
         <v>9</v>
@@ -4191,10 +4200,10 @@
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B59" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C59">
         <v>2</v>
@@ -4249,7 +4258,7 @@
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B64" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C64">
         <v>2</v>
@@ -4263,13 +4272,13 @@
     </row>
     <row r="65" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B65" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C65">
         <v>3</v>
       </c>
       <c r="D65" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="66" spans="2:12" x14ac:dyDescent="0.25">
@@ -4280,7 +4289,7 @@
         <v>3</v>
       </c>
       <c r="D66" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E66" t="s">
         <v>21</v>
@@ -4289,10 +4298,10 @@
         <v>76</v>
       </c>
       <c r="H66" t="s">
+        <v>368</v>
+      </c>
+      <c r="I66" t="s">
         <v>369</v>
-      </c>
-      <c r="I66" t="s">
-        <v>370</v>
       </c>
       <c r="J66" t="s">
         <v>42</v>
@@ -4309,49 +4318,49 @@
         <v>3</v>
       </c>
       <c r="D67" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="G67" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="68" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B68" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C68">
         <v>3</v>
       </c>
       <c r="D68" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H68" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="69" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B69" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C69">
         <v>3</v>
       </c>
       <c r="D69" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="70" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B70" t="s">
+        <v>350</v>
+      </c>
+      <c r="C70">
+        <v>3</v>
+      </c>
+      <c r="D70" t="s">
+        <v>285</v>
+      </c>
+      <c r="G70" t="s">
         <v>351</v>
-      </c>
-      <c r="C70">
-        <v>3</v>
-      </c>
-      <c r="D70" t="s">
-        <v>286</v>
-      </c>
-      <c r="G70" t="s">
-        <v>352</v>
       </c>
     </row>
     <row r="71" spans="2:12" x14ac:dyDescent="0.25">
@@ -4362,43 +4371,43 @@
         <v>3</v>
       </c>
       <c r="D71" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="G71" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="72" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B72" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C72">
         <v>3</v>
       </c>
       <c r="D72" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="73" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B73" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C73">
         <v>3</v>
       </c>
       <c r="D73" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="74" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B74" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C74">
         <v>3</v>
       </c>
       <c r="D74" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="75" spans="2:12" x14ac:dyDescent="0.25">
@@ -4414,7 +4423,7 @@
     </row>
     <row r="76" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B76" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C76">
         <v>3</v>
@@ -4425,7 +4434,7 @@
     </row>
     <row r="77" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B77" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C77">
         <v>3</v>
@@ -4447,7 +4456,7 @@
     </row>
     <row r="79" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B79" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C79">
         <v>3</v>
@@ -4502,7 +4511,7 @@
     </row>
     <row r="84" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B84" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C84">
         <v>3</v>
@@ -4513,221 +4522,218 @@
     </row>
     <row r="85" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B85" t="s">
-        <v>264</v>
+        <v>434</v>
       </c>
       <c r="C85">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D85" t="s">
-        <v>435</v>
+        <v>108</v>
       </c>
     </row>
     <row r="86" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B86" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="C86">
         <v>3</v>
       </c>
       <c r="D86" t="s">
-        <v>435</v>
-      </c>
-      <c r="H86" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
     </row>
     <row r="87" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B87" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C87">
         <v>3</v>
       </c>
       <c r="D87" t="s">
-        <v>435</v>
+        <v>434</v>
+      </c>
+      <c r="H87" t="s">
+        <v>438</v>
       </c>
     </row>
     <row r="88" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B88" t="s">
-        <v>62</v>
+        <v>259</v>
       </c>
       <c r="C88">
         <v>3</v>
       </c>
       <c r="D88" t="s">
-        <v>435</v>
-      </c>
-      <c r="H88" t="s">
-        <v>100</v>
+        <v>434</v>
       </c>
     </row>
     <row r="89" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B89" t="s">
-        <v>285</v>
+        <v>62</v>
       </c>
       <c r="C89">
         <v>3</v>
       </c>
       <c r="D89" t="s">
-        <v>435</v>
+        <v>434</v>
+      </c>
+      <c r="H89" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="90" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B90" t="s">
-        <v>266</v>
+        <v>284</v>
       </c>
       <c r="C90">
         <v>3</v>
       </c>
       <c r="D90" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="91" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B91" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C91">
         <v>3</v>
       </c>
       <c r="D91" t="s">
-        <v>435</v>
-      </c>
-      <c r="H91" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
     </row>
     <row r="92" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B92" t="s">
-        <v>344</v>
+        <v>267</v>
       </c>
       <c r="C92">
         <v>3</v>
       </c>
       <c r="D92" t="s">
-        <v>435</v>
+        <v>434</v>
+      </c>
+      <c r="H92" t="s">
+        <v>436</v>
       </c>
     </row>
     <row r="93" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B93" t="s">
-        <v>153</v>
+        <v>343</v>
       </c>
       <c r="C93">
         <v>3</v>
       </c>
       <c r="D93" t="s">
-        <v>435</v>
-      </c>
-      <c r="H93" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="94" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B94" t="s">
-        <v>58</v>
+        <v>153</v>
       </c>
       <c r="C94">
         <v>3</v>
       </c>
       <c r="D94" t="s">
+        <v>434</v>
+      </c>
+      <c r="H94" t="s">
         <v>435</v>
-      </c>
-      <c r="L94" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="95" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B95" t="s">
-        <v>304</v>
+        <v>58</v>
       </c>
       <c r="C95">
         <v>3</v>
       </c>
       <c r="D95" t="s">
-        <v>435</v>
-      </c>
-      <c r="G95" t="s">
-        <v>305</v>
+        <v>434</v>
+      </c>
+      <c r="L95" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="96" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B96" t="s">
-        <v>63</v>
+        <v>303</v>
       </c>
       <c r="C96">
         <v>3</v>
       </c>
       <c r="D96" t="s">
-        <v>435</v>
-      </c>
-      <c r="H96" t="s">
-        <v>438</v>
+        <v>434</v>
+      </c>
+      <c r="G96" t="s">
+        <v>304</v>
       </c>
     </row>
     <row r="97" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B97" t="s">
-        <v>273</v>
+        <v>63</v>
       </c>
       <c r="C97">
         <v>3</v>
       </c>
       <c r="D97" t="s">
-        <v>435</v>
+        <v>434</v>
+      </c>
+      <c r="H97" t="s">
+        <v>437</v>
       </c>
     </row>
     <row r="98" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B98" t="s">
-        <v>440</v>
+        <v>273</v>
       </c>
       <c r="C98">
         <v>3</v>
       </c>
       <c r="D98" t="s">
-        <v>55</v>
+        <v>434</v>
       </c>
     </row>
     <row r="99" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B99" t="s">
-        <v>441</v>
+        <v>492</v>
       </c>
       <c r="C99">
         <v>3</v>
       </c>
       <c r="D99" t="s">
-        <v>55</v>
-      </c>
-      <c r="L99" t="s">
-        <v>106</v>
+        <v>434</v>
       </c>
     </row>
     <row r="100" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B100" t="s">
-        <v>196</v>
+        <v>439</v>
       </c>
       <c r="C100">
         <v>3</v>
       </c>
       <c r="D100" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
     </row>
     <row r="101" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B101" t="s">
-        <v>88</v>
+        <v>440</v>
       </c>
       <c r="C101">
         <v>3</v>
       </c>
       <c r="D101" t="s">
-        <v>49</v>
-      </c>
-      <c r="I101" t="s">
-        <v>394</v>
+        <v>55</v>
+      </c>
+      <c r="L101" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="102" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B102" t="s">
-        <v>169</v>
+        <v>196</v>
       </c>
       <c r="C102">
         <v>3</v>
@@ -4738,7 +4744,7 @@
     </row>
     <row r="103" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B103" t="s">
-        <v>131</v>
+        <v>88</v>
       </c>
       <c r="C103">
         <v>3</v>
@@ -4746,10 +4752,13 @@
       <c r="D103" t="s">
         <v>49</v>
       </c>
+      <c r="I103" t="s">
+        <v>393</v>
+      </c>
     </row>
     <row r="104" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B104" t="s">
-        <v>14</v>
+        <v>169</v>
       </c>
       <c r="C104">
         <v>3</v>
@@ -4757,28 +4766,10 @@
       <c r="D104" t="s">
         <v>49</v>
       </c>
-      <c r="E104" t="s">
-        <v>95</v>
-      </c>
-      <c r="F104" t="s">
-        <v>90</v>
-      </c>
-      <c r="H104" t="s">
-        <v>40</v>
-      </c>
-      <c r="I104" t="s">
-        <v>405</v>
-      </c>
-      <c r="J104" t="s">
-        <v>77</v>
-      </c>
-      <c r="K104" t="s">
-        <v>19</v>
-      </c>
     </row>
     <row r="105" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B105" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C105">
         <v>3</v>
@@ -4789,7 +4780,7 @@
     </row>
     <row r="106" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B106" t="s">
-        <v>251</v>
+        <v>14</v>
       </c>
       <c r="C106">
         <v>3</v>
@@ -4797,10 +4788,28 @@
       <c r="D106" t="s">
         <v>49</v>
       </c>
+      <c r="E106" t="s">
+        <v>95</v>
+      </c>
+      <c r="F106" t="s">
+        <v>90</v>
+      </c>
+      <c r="H106" t="s">
+        <v>40</v>
+      </c>
+      <c r="I106" t="s">
+        <v>404</v>
+      </c>
+      <c r="J106" t="s">
+        <v>77</v>
+      </c>
+      <c r="K106" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="107" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B107" t="s">
-        <v>263</v>
+        <v>132</v>
       </c>
       <c r="C107">
         <v>3</v>
@@ -4811,29 +4820,29 @@
     </row>
     <row r="108" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B108" t="s">
-        <v>134</v>
+        <v>251</v>
       </c>
       <c r="C108">
         <v>3</v>
       </c>
       <c r="D108" t="s">
-        <v>130</v>
+        <v>49</v>
       </c>
     </row>
     <row r="109" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B109" t="s">
-        <v>135</v>
+        <v>263</v>
       </c>
       <c r="C109">
         <v>3</v>
       </c>
       <c r="D109" t="s">
-        <v>130</v>
+        <v>49</v>
       </c>
     </row>
     <row r="110" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B110" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C110">
         <v>3</v>
@@ -4844,29 +4853,29 @@
     </row>
     <row r="111" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B111" t="s">
-        <v>209</v>
+        <v>135</v>
       </c>
       <c r="C111">
         <v>3</v>
       </c>
       <c r="D111" t="s">
-        <v>67</v>
+        <v>130</v>
       </c>
     </row>
     <row r="112" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B112" t="s">
-        <v>312</v>
+        <v>133</v>
       </c>
       <c r="C112">
         <v>3</v>
       </c>
       <c r="D112" t="s">
-        <v>67</v>
+        <v>130</v>
       </c>
     </row>
     <row r="113" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B113" t="s">
-        <v>116</v>
+        <v>209</v>
       </c>
       <c r="C113">
         <v>3</v>
@@ -4877,7 +4886,7 @@
     </row>
     <row r="114" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B114" t="s">
-        <v>220</v>
+        <v>311</v>
       </c>
       <c r="C114">
         <v>3</v>
@@ -4888,29 +4897,29 @@
     </row>
     <row r="115" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B115" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="C115">
         <v>3</v>
       </c>
       <c r="D115" t="s">
-        <v>119</v>
+        <v>67</v>
       </c>
     </row>
     <row r="116" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B116" t="s">
-        <v>136</v>
+        <v>220</v>
       </c>
       <c r="C116">
         <v>3</v>
       </c>
       <c r="D116" t="s">
-        <v>119</v>
+        <v>67</v>
       </c>
     </row>
     <row r="117" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B117" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C117">
         <v>3</v>
@@ -4921,7 +4930,7 @@
     </row>
     <row r="118" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B118" t="s">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="C118">
         <v>3</v>
@@ -4932,7 +4941,7 @@
     </row>
     <row r="119" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B119" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C119">
         <v>3</v>
@@ -4943,109 +4952,109 @@
     </row>
     <row r="120" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B120" t="s">
-        <v>198</v>
+        <v>122</v>
       </c>
       <c r="C120">
         <v>3</v>
       </c>
       <c r="D120" t="s">
-        <v>70</v>
+        <v>119</v>
       </c>
     </row>
     <row r="121" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B121" t="s">
-        <v>71</v>
+        <v>121</v>
       </c>
       <c r="C121">
         <v>3</v>
       </c>
       <c r="D121" t="s">
-        <v>70</v>
-      </c>
-      <c r="I121" t="s">
-        <v>404</v>
+        <v>119</v>
       </c>
     </row>
     <row r="122" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B122" t="s">
-        <v>360</v>
+        <v>198</v>
       </c>
       <c r="C122">
         <v>3</v>
       </c>
       <c r="D122" t="s">
-        <v>276</v>
+        <v>70</v>
       </c>
     </row>
     <row r="123" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B123" t="s">
-        <v>331</v>
+        <v>71</v>
       </c>
       <c r="C123">
         <v>3</v>
       </c>
       <c r="D123" t="s">
-        <v>152</v>
+        <v>70</v>
+      </c>
+      <c r="I123" t="s">
+        <v>403</v>
       </c>
     </row>
     <row r="124" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B124" t="s">
-        <v>68</v>
+        <v>359</v>
       </c>
       <c r="C124">
         <v>3</v>
       </c>
       <c r="D124" t="s">
-        <v>173</v>
+        <v>276</v>
       </c>
     </row>
     <row r="125" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B125" t="s">
-        <v>258</v>
+        <v>330</v>
       </c>
       <c r="C125">
         <v>3</v>
       </c>
       <c r="D125" t="s">
-        <v>173</v>
+        <v>152</v>
       </c>
     </row>
     <row r="126" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B126" t="s">
-        <v>284</v>
+        <v>68</v>
       </c>
       <c r="C126">
         <v>3</v>
       </c>
       <c r="D126" t="s">
-        <v>144</v>
+        <v>173</v>
       </c>
     </row>
     <row r="127" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B127" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="C127">
         <v>3</v>
       </c>
       <c r="D127" t="s">
-        <v>144</v>
+        <v>173</v>
       </c>
     </row>
     <row r="128" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B128" t="s">
-        <v>138</v>
+        <v>255</v>
       </c>
       <c r="C128">
         <v>3</v>
       </c>
       <c r="D128" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
     </row>
     <row r="129" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B129" t="s">
-        <v>75</v>
+        <v>138</v>
       </c>
       <c r="C129">
         <v>3</v>
@@ -5056,18 +5065,18 @@
     </row>
     <row r="130" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B130" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="C130">
         <v>3</v>
       </c>
       <c r="D130" t="s">
-        <v>9</v>
+        <v>137</v>
       </c>
     </row>
     <row r="131" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B131" t="s">
-        <v>10</v>
+        <v>82</v>
       </c>
       <c r="C131">
         <v>3</v>
@@ -5075,19 +5084,10 @@
       <c r="D131" t="s">
         <v>9</v>
       </c>
-      <c r="E131" t="s">
-        <v>112</v>
-      </c>
-      <c r="F131" t="s">
-        <v>113</v>
-      </c>
-      <c r="H131" t="s">
-        <v>81</v>
-      </c>
     </row>
     <row r="132" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B132" t="s">
-        <v>174</v>
+        <v>10</v>
       </c>
       <c r="C132">
         <v>3</v>
@@ -5095,10 +5095,19 @@
       <c r="D132" t="s">
         <v>9</v>
       </c>
+      <c r="E132" t="s">
+        <v>112</v>
+      </c>
+      <c r="F132" t="s">
+        <v>113</v>
+      </c>
+      <c r="H132" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="133" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B133" t="s">
-        <v>201</v>
+        <v>174</v>
       </c>
       <c r="C133">
         <v>3</v>
@@ -5109,18 +5118,18 @@
     </row>
     <row r="134" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B134" t="s">
-        <v>146</v>
+        <v>201</v>
       </c>
       <c r="C134">
         <v>3</v>
       </c>
       <c r="D134" t="s">
-        <v>213</v>
+        <v>9</v>
       </c>
     </row>
     <row r="135" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B135" t="s">
-        <v>215</v>
+        <v>146</v>
       </c>
       <c r="C135">
         <v>3</v>
@@ -5131,7 +5140,7 @@
     </row>
     <row r="136" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B136" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C136">
         <v>3</v>
@@ -5142,29 +5151,29 @@
     </row>
     <row r="137" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B137" t="s">
-        <v>329</v>
+        <v>214</v>
       </c>
       <c r="C137">
         <v>3</v>
       </c>
       <c r="D137" t="s">
-        <v>345</v>
+        <v>213</v>
       </c>
     </row>
     <row r="138" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B138" t="s">
-        <v>249</v>
+        <v>328</v>
       </c>
       <c r="C138">
         <v>3</v>
       </c>
       <c r="D138" t="s">
-        <v>72</v>
+        <v>344</v>
       </c>
     </row>
     <row r="139" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B139" t="s">
-        <v>74</v>
+        <v>249</v>
       </c>
       <c r="C139">
         <v>3</v>
@@ -5175,7 +5184,7 @@
     </row>
     <row r="140" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B140" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C140">
         <v>3</v>
@@ -5186,7 +5195,7 @@
     </row>
     <row r="141" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B141" t="s">
-        <v>250</v>
+        <v>73</v>
       </c>
       <c r="C141">
         <v>3</v>
@@ -5197,18 +5206,18 @@
     </row>
     <row r="142" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B142" t="s">
-        <v>61</v>
+        <v>250</v>
       </c>
       <c r="C142">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D142" t="s">
-        <v>267</v>
+        <v>72</v>
       </c>
     </row>
     <row r="143" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B143" t="s">
-        <v>386</v>
+        <v>61</v>
       </c>
       <c r="C143">
         <v>4</v>
@@ -5219,18 +5228,18 @@
     </row>
     <row r="144" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B144" t="s">
-        <v>203</v>
+        <v>385</v>
       </c>
       <c r="C144">
         <v>4</v>
       </c>
       <c r="D144" t="s">
-        <v>198</v>
+        <v>267</v>
       </c>
     </row>
     <row r="145" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B145" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C145">
         <v>4</v>
@@ -5241,106 +5250,106 @@
     </row>
     <row r="146" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B146" t="s">
-        <v>56</v>
+        <v>204</v>
       </c>
       <c r="C146">
         <v>4</v>
       </c>
       <c r="D146" t="s">
-        <v>440</v>
+        <v>198</v>
       </c>
     </row>
     <row r="147" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B147" t="s">
-        <v>107</v>
+        <v>56</v>
       </c>
       <c r="C147">
         <v>4</v>
       </c>
       <c r="D147" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="148" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B148" t="s">
-        <v>315</v>
+        <v>107</v>
       </c>
       <c r="C148">
         <v>4</v>
       </c>
       <c r="D148" t="s">
-        <v>314</v>
+        <v>439</v>
       </c>
     </row>
     <row r="149" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B149" t="s">
-        <v>57</v>
+        <v>314</v>
       </c>
       <c r="C149">
         <v>4</v>
       </c>
       <c r="D149" t="s">
-        <v>441</v>
+        <v>313</v>
       </c>
     </row>
     <row r="150" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B150" t="s">
-        <v>115</v>
+        <v>57</v>
       </c>
       <c r="C150">
         <v>4</v>
       </c>
       <c r="D150" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="151" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B151" t="s">
-        <v>237</v>
+        <v>115</v>
       </c>
       <c r="C151">
         <v>4</v>
       </c>
       <c r="D151" t="s">
-        <v>304</v>
+        <v>440</v>
       </c>
     </row>
     <row r="152" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B152" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C152">
         <v>4</v>
       </c>
       <c r="D152" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="153" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B153" t="s">
-        <v>305</v>
+        <v>236</v>
       </c>
       <c r="C153">
         <v>4</v>
       </c>
       <c r="D153" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="154" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B154" t="s">
-        <v>223</v>
+        <v>304</v>
       </c>
       <c r="C154">
         <v>4</v>
       </c>
       <c r="D154" t="s">
-        <v>11</v>
+        <v>303</v>
       </c>
     </row>
     <row r="155" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B155" t="s">
-        <v>202</v>
+        <v>223</v>
       </c>
       <c r="C155">
         <v>4</v>
@@ -5351,7 +5360,7 @@
     </row>
     <row r="156" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B156" t="s">
-        <v>225</v>
+        <v>202</v>
       </c>
       <c r="C156">
         <v>4</v>
@@ -5362,7 +5371,7 @@
     </row>
     <row r="157" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B157" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C157">
         <v>4</v>
@@ -5373,18 +5382,18 @@
     </row>
     <row r="158" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B158" t="s">
-        <v>270</v>
+        <v>224</v>
       </c>
       <c r="C158">
         <v>4</v>
       </c>
       <c r="D158" t="s">
-        <v>132</v>
+        <v>11</v>
       </c>
     </row>
     <row r="159" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B159" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C159">
         <v>4</v>
@@ -5395,19 +5404,18 @@
     </row>
     <row r="160" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B160" t="s">
+        <v>269</v>
+      </c>
+      <c r="C160">
+        <v>4</v>
+      </c>
+      <c r="D160" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="161" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="B161" t="s">
         <v>66</v>
-      </c>
-      <c r="C160">
-        <v>5</v>
-      </c>
-      <c r="D160" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="161" spans="1:24" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A161"/>
-      <c r="B161" t="s">
-        <v>65</v>
       </c>
       <c r="C161">
         <v>5</v>
@@ -5415,21 +5423,11 @@
       <c r="D161" t="s">
         <v>61</v>
       </c>
-      <c r="E161"/>
-      <c r="F161"/>
-      <c r="G161"/>
-      <c r="H161"/>
-      <c r="I161"/>
-      <c r="J161"/>
-      <c r="K161"/>
-      <c r="L161" t="s">
-        <v>103</v>
-      </c>
-      <c r="M161"/>
-    </row>
-    <row r="162" spans="1:24" x14ac:dyDescent="0.25">
+    </row>
+    <row r="162" spans="1:24" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A162"/>
       <c r="B162" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C162">
         <v>5</v>
@@ -5437,26 +5435,48 @@
       <c r="D162" t="s">
         <v>61</v>
       </c>
-      <c r="N162" s="12"/>
-      <c r="O162" s="12"/>
-      <c r="P162" s="12"/>
-      <c r="Q162" s="12"/>
-      <c r="R162" s="12"/>
-      <c r="S162" s="12"/>
-      <c r="T162" s="12"/>
-      <c r="U162" s="12"/>
-      <c r="V162" s="12"/>
-      <c r="W162" s="12"/>
-      <c r="X162" s="12"/>
+      <c r="E162"/>
+      <c r="F162"/>
+      <c r="G162"/>
+      <c r="H162"/>
+      <c r="I162"/>
+      <c r="J162"/>
+      <c r="K162"/>
+      <c r="L162" t="s">
+        <v>103</v>
+      </c>
+      <c r="M162"/>
     </row>
     <row r="163" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B163" t="s">
+        <v>64</v>
+      </c>
+      <c r="C163">
+        <v>5</v>
+      </c>
+      <c r="D163" t="s">
+        <v>61</v>
+      </c>
+      <c r="N163" s="12"/>
+      <c r="O163" s="12"/>
+      <c r="P163" s="12"/>
+      <c r="Q163" s="12"/>
+      <c r="R163" s="12"/>
+      <c r="S163" s="12"/>
+      <c r="T163" s="12"/>
+      <c r="U163" s="12"/>
+      <c r="V163" s="12"/>
+      <c r="W163" s="12"/>
+      <c r="X163" s="12"/>
+    </row>
+    <row r="164" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="B164" t="s">
         <v>152</v>
       </c>
-      <c r="C163">
-        <v>2</v>
-      </c>
-      <c r="D163" t="s">
+      <c r="C164">
+        <v>2</v>
+      </c>
+      <c r="D164" t="s">
         <v>108</v>
       </c>
     </row>
@@ -5474,17 +5494,17 @@
     <hyperlink ref="I18" r:id="rId10" xr:uid="{BBE13F30-5D0F-4CB4-8E9E-6CB2653C1525}"/>
     <hyperlink ref="I54" r:id="rId11" xr:uid="{E4E35AF7-6540-49D7-A672-7C6E532CD1F1}"/>
     <hyperlink ref="J66" r:id="rId12" xr:uid="{BB046B94-7D2F-437A-A2D9-44D95E8F73A4}"/>
-    <hyperlink ref="J104" r:id="rId13" xr:uid="{8821C060-D793-4720-93F0-4C72E3693803}"/>
+    <hyperlink ref="J106" r:id="rId13" xr:uid="{8821C060-D793-4720-93F0-4C72E3693803}"/>
     <hyperlink ref="L66" r:id="rId14" display="https://www.ne.se/uppslagsverk/encyklopedi/l%C3%A5ng/grophus?isSearchResult=true" xr:uid="{6FC02FFC-21E6-45DD-9A5D-665E3F679971}"/>
-    <hyperlink ref="L99" r:id="rId15" display="https://www.ne.se/uppslagsverk/encyklopedi/l%C3%A5ng/skelettgrav" xr:uid="{F1F627A7-75B9-40A6-8300-13646868BC53}"/>
-    <hyperlink ref="L94" r:id="rId16" xr:uid="{DDCD8050-28A0-4307-82D8-B072C3A6803A}"/>
+    <hyperlink ref="L101" r:id="rId15" display="https://www.ne.se/uppslagsverk/encyklopedi/l%C3%A5ng/skelettgrav" xr:uid="{F1F627A7-75B9-40A6-8300-13646868BC53}"/>
+    <hyperlink ref="L95" r:id="rId16" xr:uid="{DDCD8050-28A0-4307-82D8-B072C3A6803A}"/>
     <hyperlink ref="I66" r:id="rId17" xr:uid="{E018BDD7-78F6-4568-981B-7331D5BFC411}"/>
     <hyperlink ref="I26" r:id="rId18" xr:uid="{3748A75A-39CA-4B0B-8A58-344DAB0526CA}"/>
     <hyperlink ref="I17" r:id="rId19" xr:uid="{41790389-35E4-42A0-90A5-7D3715963227}"/>
-    <hyperlink ref="I101" r:id="rId20" xr:uid="{00814DC3-A074-4D0E-82BC-F3875AF0973F}"/>
-    <hyperlink ref="L161" r:id="rId21" display="https://www.ne.se/uppslagsverk/encyklopedi/l%C3%A5ng/g%C3%A5nggrift?isSearchResult=true" xr:uid="{7CEAE847-3129-4429-8248-288FF45D196E}"/>
-    <hyperlink ref="I121" r:id="rId22" xr:uid="{291D0B36-C7DC-4BC9-8BEB-B3FA2B2F402B}"/>
-    <hyperlink ref="I104" r:id="rId23" xr:uid="{BA1FC5A2-C85A-4054-8535-113375B6188E}"/>
+    <hyperlink ref="I103" r:id="rId20" xr:uid="{00814DC3-A074-4D0E-82BC-F3875AF0973F}"/>
+    <hyperlink ref="L162" r:id="rId21" display="https://www.ne.se/uppslagsverk/encyklopedi/l%C3%A5ng/g%C3%A5nggrift?isSearchResult=true" xr:uid="{7CEAE847-3129-4429-8248-288FF45D196E}"/>
+    <hyperlink ref="I123" r:id="rId22" xr:uid="{291D0B36-C7DC-4BC9-8BEB-B3FA2B2F402B}"/>
+    <hyperlink ref="I106" r:id="rId23" xr:uid="{BA1FC5A2-C85A-4054-8535-113375B6188E}"/>
     <hyperlink ref="I38" r:id="rId24" xr:uid="{E281957A-D8F9-4D7C-AACA-7C970B17F40E}"/>
     <hyperlink ref="J25" r:id="rId25" xr:uid="{1920DECD-4998-4F1D-851B-75ABEE4925AB}"/>
   </hyperlinks>
@@ -5517,56 +5537,56 @@
   <sheetData>
     <row r="1" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C1" t="s">
         <v>257</v>
       </c>
       <c r="D1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="E1" t="s">
+        <v>443</v>
+      </c>
+      <c r="F1" t="s">
         <v>444</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>445</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>446</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
+        <v>461</v>
+      </c>
+      <c r="J1" t="s">
+        <v>450</v>
+      </c>
+      <c r="K1" t="s">
         <v>447</v>
       </c>
-      <c r="I1" t="s">
-        <v>462</v>
-      </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
+        <v>448</v>
+      </c>
+      <c r="M1" t="s">
         <v>451</v>
-      </c>
-      <c r="K1" t="s">
-        <v>448</v>
-      </c>
-      <c r="L1" t="s">
-        <v>449</v>
-      </c>
-      <c r="M1" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12"/>
       <c r="B2" s="14" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C2" s="14">
         <v>0</v>
       </c>
       <c r="D2" s="10"/>
       <c r="E2" s="14" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="F2" s="13"/>
       <c r="G2" s="13"/>
@@ -5579,7 +5599,7 @@
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>4</v>
@@ -5588,10 +5608,10 @@
         <v>1</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="F3" s="7" t="s">
         <v>96</v>
@@ -5606,7 +5626,7 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B4" s="7" t="s">
         <v>3</v>
@@ -5618,7 +5638,7 @@
         <v>4</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="F4" s="7"/>
       <c r="G4" s="7"/>
@@ -5635,7 +5655,7 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B5" s="7" t="s">
         <v>2</v>
@@ -5647,7 +5667,7 @@
         <v>4</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="F5" s="7" t="s">
         <v>114</v>
@@ -5664,7 +5684,7 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>1</v>
@@ -5691,7 +5711,7 @@
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B7" s="7" t="s">
         <v>0</v>
@@ -5721,7 +5741,7 @@
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="12"/>
       <c r="B8" s="7" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C8" s="7">
         <v>3</v>
@@ -5742,7 +5762,7 @@
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="12"/>
       <c r="B9" s="7" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C9" s="7">
         <v>3</v>
@@ -5755,7 +5775,7 @@
       <c r="G9" s="7"/>
       <c r="H9" s="7"/>
       <c r="I9" s="9" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="J9" s="7"/>
       <c r="K9" s="7"/>
@@ -5839,11 +5859,11 @@
         <v>2</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="F13" s="7"/>
       <c r="G13" s="7" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H13" s="7"/>
       <c r="I13" s="7"/>
@@ -5864,7 +5884,7 @@
         <v>2</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="F14" s="7"/>
       <c r="G14" s="7"/>
@@ -5893,7 +5913,7 @@
       <c r="I15" s="7"/>
       <c r="J15" s="7"/>
       <c r="K15" s="7" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="L15" s="7"/>
       <c r="M15" s="7"/>
@@ -6040,11 +6060,11 @@
         <v>2</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="F22" s="7"/>
       <c r="G22" s="7" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H22" s="7"/>
       <c r="I22" s="7"/>
@@ -6098,7 +6118,7 @@
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="12"/>
       <c r="B25" s="7" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C25" s="7">
         <v>3</v>
@@ -6163,7 +6183,7 @@
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" s="12"/>
       <c r="B28" s="7" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C28" s="7">
         <v>3</v>
@@ -6184,7 +6204,7 @@
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" s="12"/>
       <c r="B29" s="7" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C29" s="7">
         <v>3</v>
@@ -6226,7 +6246,7 @@
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" s="12"/>
       <c r="B31" s="7" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C31" s="7">
         <v>3</v>
@@ -6289,7 +6309,7 @@
     <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" s="12"/>
       <c r="B34" s="7" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C34" s="7">
         <v>3</v>
@@ -6352,7 +6372,7 @@
     <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" s="12"/>
       <c r="B37" s="7" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C37" s="7">
         <v>3</v>
@@ -6373,7 +6393,7 @@
     <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" s="12"/>
       <c r="B38" s="7" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C38" s="7">
         <v>3</v>
@@ -6394,7 +6414,7 @@
     <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" s="12"/>
       <c r="B39" s="7" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C39" s="7">
         <v>3</v>
@@ -6415,7 +6435,7 @@
     <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" s="12"/>
       <c r="B40" s="7" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C40" s="7">
         <v>3</v>
@@ -6426,7 +6446,7 @@
       <c r="E40" s="7"/>
       <c r="F40" s="7"/>
       <c r="G40" s="7" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H40" s="7"/>
       <c r="I40" s="7"/>
@@ -6438,7 +6458,7 @@
     <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" s="12"/>
       <c r="B41" s="7" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C41" s="7">
         <v>3</v>
@@ -6459,7 +6479,7 @@
     <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" s="12"/>
       <c r="B42" s="7" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C42" s="7">
         <v>3</v>
@@ -6480,7 +6500,7 @@
     <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" s="12"/>
       <c r="B43" s="7" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C43" s="7">
         <v>3</v>
@@ -6504,7 +6524,7 @@
         <v>232</v>
       </c>
       <c r="C44" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D44" s="8" t="s">
         <v>180</v>
@@ -6525,7 +6545,7 @@
         <v>53</v>
       </c>
       <c r="C45" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D45" s="8" t="s">
         <v>180</v>
@@ -6546,7 +6566,7 @@
         <v>54</v>
       </c>
       <c r="C46" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D46" s="8" t="s">
         <v>180</v>
@@ -6567,7 +6587,7 @@
         <v>233</v>
       </c>
       <c r="C47" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D47" s="8" t="s">
         <v>180</v>
@@ -6588,7 +6608,7 @@
         <v>234</v>
       </c>
       <c r="C48" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D48" s="8" t="s">
         <v>180</v>
@@ -6609,7 +6629,7 @@
         <v>235</v>
       </c>
       <c r="C49" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D49" s="8" t="s">
         <v>180</v>
@@ -6630,13 +6650,13 @@
         <v>268</v>
       </c>
       <c r="C50" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D50" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E50" s="12"/>
-      <c r="F50" s="12"/>
+      <c r="F50" s="17"/>
       <c r="G50" s="12"/>
       <c r="H50" s="12"/>
       <c r="I50" s="12"/>
@@ -6651,7 +6671,7 @@
         <v>272</v>
       </c>
       <c r="C51" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D51" s="8" t="s">
         <v>180</v>
@@ -6672,7 +6692,7 @@
         <v>277</v>
       </c>
       <c r="C52" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D52" s="8" t="s">
         <v>180</v>
@@ -6693,7 +6713,7 @@
         <v>281</v>
       </c>
       <c r="C53" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D53" s="8" t="s">
         <v>180</v>
@@ -6714,7 +6734,7 @@
         <v>274</v>
       </c>
       <c r="C54" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D54" s="8" t="s">
         <v>180</v>
@@ -6795,7 +6815,7 @@
     <row r="58" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A58" s="12"/>
       <c r="B58" s="7" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C58" s="7">
         <v>3</v>
@@ -6837,7 +6857,7 @@
     <row r="60" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A60" s="12"/>
       <c r="B60" s="7" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C60" s="7">
         <v>3</v>
@@ -6846,7 +6866,7 @@
         <v>1</v>
       </c>
       <c r="E60" s="7" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="F60" s="7"/>
       <c r="G60" s="7"/>
@@ -6944,7 +6964,7 @@
     <row r="65" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A65" s="12"/>
       <c r="B65" s="7" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C65" s="7">
         <v>3</v>
@@ -7018,7 +7038,7 @@
       <c r="E68" s="7"/>
       <c r="F68" s="7"/>
       <c r="G68" s="7" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H68" s="7"/>
       <c r="I68" s="7"/>
@@ -7030,7 +7050,7 @@
     <row r="69" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A69" s="12"/>
       <c r="B69" s="7" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C69" s="7">
         <v>3</v>
@@ -7051,7 +7071,7 @@
     <row r="70" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A70" s="12"/>
       <c r="B70" s="7" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C70" s="7">
         <v>3</v>
@@ -7093,7 +7113,7 @@
     <row r="72" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A72" s="12"/>
       <c r="B72" s="7" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C72" s="7">
         <v>3</v>
@@ -7148,56 +7168,56 @@
   <sheetData>
     <row r="1" spans="1:13" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C1" t="s">
         <v>257</v>
       </c>
       <c r="D1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="E1" t="s">
+        <v>443</v>
+      </c>
+      <c r="F1" t="s">
         <v>444</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>445</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>446</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
+        <v>461</v>
+      </c>
+      <c r="J1" t="s">
+        <v>450</v>
+      </c>
+      <c r="K1" t="s">
         <v>447</v>
       </c>
-      <c r="I1" t="s">
-        <v>462</v>
-      </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
+        <v>448</v>
+      </c>
+      <c r="M1" t="s">
         <v>451</v>
-      </c>
-      <c r="K1" t="s">
-        <v>448</v>
-      </c>
-      <c r="L1" t="s">
-        <v>449</v>
-      </c>
-      <c r="M1" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7"/>
       <c r="B2" s="8" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C2" s="14">
         <v>0</v>
       </c>
       <c r="D2" s="10"/>
       <c r="E2" s="14" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="F2" s="14"/>
       <c r="G2" s="14"/>
@@ -7210,16 +7230,16 @@
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C3" s="7">
         <v>1</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>97</v>
@@ -7237,7 +7257,7 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B4" s="7" t="s">
         <v>83</v>
@@ -7246,7 +7266,7 @@
         <v>2</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>85</v>
@@ -7269,7 +7289,7 @@
         <v>2</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="E5" s="7"/>
       <c r="F5" s="7"/>
@@ -7290,16 +7310,16 @@
         <v>2</v>
       </c>
       <c r="D6" s="7" t="s">
+        <v>464</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>486</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>487</v>
+      </c>
+      <c r="G6" s="7" t="s">
         <v>465</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>487</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>488</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>466</v>
       </c>
       <c r="H6" s="7"/>
       <c r="I6" s="7"/>
@@ -7313,19 +7333,19 @@
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="7"/>
       <c r="B7" s="7" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C7" s="7">
         <v>2</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="E7" s="7"/>
       <c r="F7" s="7"/>
       <c r="G7" s="7"/>
       <c r="H7" s="7" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I7" s="7"/>
       <c r="J7" s="7"/>
@@ -7336,13 +7356,13 @@
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="7"/>
       <c r="B8" s="7" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C8" s="7">
         <v>2</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="E8" s="7"/>
       <c r="F8" s="7"/>
@@ -7363,7 +7383,7 @@
         <v>2</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="E9" s="7"/>
       <c r="F9" s="7"/>
@@ -7384,7 +7404,7 @@
         <v>2</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>38</v>
@@ -7411,7 +7431,7 @@
         <v>2</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="E11" s="7" t="s">
         <v>105</v>
@@ -7432,7 +7452,7 @@
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="7"/>
       <c r="B12" s="7" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C12" s="7">
         <v>3</v>
@@ -7453,7 +7473,7 @@
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="7"/>
       <c r="B13" s="7" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C13" s="7">
         <v>3</v>
@@ -7516,7 +7536,7 @@
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" s="7"/>
       <c r="B16" s="7" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C16" s="7">
         <v>3</v>
@@ -7537,7 +7557,7 @@
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="7"/>
       <c r="B17" s="7" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C17" s="7">
         <v>3</v>
@@ -7558,7 +7578,7 @@
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="7"/>
       <c r="B18" s="7" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C18" s="7">
         <v>3</v>
@@ -7579,7 +7599,7 @@
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="7"/>
       <c r="B19" s="7" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C19" s="7">
         <v>3</v>
@@ -7600,7 +7620,7 @@
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="7"/>
       <c r="B20" s="7" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C20" s="7">
         <v>3</v>
@@ -7621,13 +7641,13 @@
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" s="7"/>
       <c r="B21" s="7" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C21" s="7">
         <v>3</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E21" s="7"/>
       <c r="F21" s="7"/>
@@ -7648,7 +7668,7 @@
         <v>3</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E22" s="7"/>
       <c r="F22" s="7"/>
@@ -7663,13 +7683,13 @@
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="7"/>
       <c r="B23" s="7" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C23" s="7">
         <v>3</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E23" s="7"/>
       <c r="F23" s="7"/>
@@ -7690,7 +7710,7 @@
         <v>3</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E24" s="7"/>
       <c r="F24" s="7"/>
@@ -7705,7 +7725,7 @@
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="7"/>
       <c r="B25" s="7" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C25" s="7">
         <v>3</v>
@@ -7717,7 +7737,7 @@
       <c r="F25" s="7"/>
       <c r="G25" s="7"/>
       <c r="H25" s="7" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="I25" s="7"/>
       <c r="J25" s="7"/>
@@ -7812,7 +7832,7 @@
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" s="7"/>
       <c r="B30" s="7" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C30" s="7">
         <v>4</v>
@@ -7833,13 +7853,13 @@
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" s="7"/>
       <c r="B31" s="7" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C31" s="7">
         <v>4</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="E31" s="7"/>
       <c r="F31" s="7"/>
@@ -7854,16 +7874,16 @@
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" s="7"/>
       <c r="B32" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="C32" s="7">
+        <v>2</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>464</v>
+      </c>
+      <c r="E32" s="7" t="s">
         <v>341</v>
-      </c>
-      <c r="C32" s="7">
-        <v>2</v>
-      </c>
-      <c r="D32" s="7" t="s">
-        <v>465</v>
-      </c>
-      <c r="E32" s="7" t="s">
-        <v>342</v>
       </c>
       <c r="F32" s="7"/>
       <c r="G32" s="7"/>
@@ -7877,16 +7897,16 @@
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" s="7"/>
       <c r="B33" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="C33" s="7">
+        <v>2</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>464</v>
+      </c>
+      <c r="E33" s="7" t="s">
         <v>339</v>
-      </c>
-      <c r="C33" s="7">
-        <v>2</v>
-      </c>
-      <c r="D33" s="7" t="s">
-        <v>465</v>
-      </c>
-      <c r="E33" s="7" t="s">
-        <v>340</v>
       </c>
       <c r="F33" s="7" t="s">
         <v>117</v>
@@ -7978,56 +7998,56 @@
   <sheetData>
     <row r="1" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C1" t="s">
         <v>257</v>
       </c>
       <c r="D1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="E1" t="s">
+        <v>443</v>
+      </c>
+      <c r="F1" t="s">
         <v>444</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>445</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>446</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
+        <v>461</v>
+      </c>
+      <c r="J1" t="s">
+        <v>450</v>
+      </c>
+      <c r="K1" t="s">
         <v>447</v>
       </c>
-      <c r="I1" t="s">
-        <v>462</v>
-      </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
+        <v>448</v>
+      </c>
+      <c r="M1" t="s">
         <v>451</v>
-      </c>
-      <c r="K1" t="s">
-        <v>448</v>
-      </c>
-      <c r="L1" t="s">
-        <v>449</v>
-      </c>
-      <c r="M1" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7"/>
       <c r="B2" s="14" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C2" s="14">
         <v>0</v>
       </c>
       <c r="D2" s="10"/>
       <c r="E2" s="14" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="F2" s="14"/>
       <c r="G2" s="14"/>
@@ -8040,7 +8060,7 @@
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>25</v>
@@ -8049,7 +8069,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>109</v>
@@ -8065,7 +8085,7 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B4" s="7" t="s">
         <v>28</v>
@@ -8088,7 +8108,7 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B5" s="7" t="s">
         <v>155</v>
@@ -8111,7 +8131,7 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>156</v>
@@ -8134,7 +8154,7 @@
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B7" s="7" t="s">
         <v>216</v>
@@ -8157,7 +8177,7 @@
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B8" s="7" t="s">
         <v>226</v>
@@ -8403,10 +8423,10 @@
       <c r="F19" s="7"/>
       <c r="G19" s="7"/>
       <c r="H19" s="7" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="I19" s="9" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="J19" s="7"/>
       <c r="K19" s="7"/>
@@ -8431,7 +8451,7 @@
         <v>245</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H20" s="7"/>
       <c r="I20" s="11" t="s">
@@ -8445,7 +8465,7 @@
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" s="7"/>
       <c r="B21" s="7" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C21" s="7">
         <v>2</v>
@@ -8466,7 +8486,7 @@
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" s="7"/>
       <c r="B22" s="7" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C22" s="7">
         <v>2</v>
@@ -8487,7 +8507,7 @@
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="7"/>
       <c r="B23" s="7" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C23" s="7">
         <v>2</v>
@@ -8517,10 +8537,10 @@
         <v>25</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="G24" s="7"/>
       <c r="H24" s="7"/>
@@ -8563,43 +8583,43 @@
   <sheetData>
     <row r="1" spans="1:13" ht="55.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C1" t="s">
         <v>257</v>
       </c>
       <c r="D1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="E1" t="s">
+        <v>443</v>
+      </c>
+      <c r="F1" t="s">
         <v>444</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>445</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>446</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
+        <v>461</v>
+      </c>
+      <c r="J1" t="s">
+        <v>450</v>
+      </c>
+      <c r="K1" t="s">
         <v>447</v>
       </c>
-      <c r="I1" t="s">
-        <v>462</v>
-      </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
+        <v>448</v>
+      </c>
+      <c r="M1" s="15" t="s">
         <v>451</v>
-      </c>
-      <c r="K1" t="s">
-        <v>448</v>
-      </c>
-      <c r="L1" t="s">
-        <v>449</v>
-      </c>
-      <c r="M1" s="15" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
@@ -8611,13 +8631,13 @@
         <v>1</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="E2" s="4"/>
       <c r="F2" s="4"/>
       <c r="G2" s="4"/>
       <c r="H2" s="4" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="I2" s="4"/>
       <c r="J2" s="4"/>
@@ -8822,48 +8842,48 @@
   <sheetData>
     <row r="1" spans="1:13" ht="50.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C1" t="s">
         <v>257</v>
       </c>
       <c r="D1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="E1" t="s">
+        <v>443</v>
+      </c>
+      <c r="F1" t="s">
         <v>444</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>445</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>446</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
+        <v>461</v>
+      </c>
+      <c r="J1" t="s">
+        <v>450</v>
+      </c>
+      <c r="K1" t="s">
         <v>447</v>
       </c>
-      <c r="I1" t="s">
-        <v>462</v>
-      </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
+        <v>448</v>
+      </c>
+      <c r="M1" s="15" t="s">
         <v>451</v>
-      </c>
-      <c r="K1" t="s">
-        <v>448</v>
-      </c>
-      <c r="L1" t="s">
-        <v>449</v>
-      </c>
-      <c r="M1" s="15" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -8872,7 +8892,7 @@
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -8880,7 +8900,7 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C4">
         <v>2</v>
@@ -8888,7 +8908,7 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C5">
         <v>2</v>
@@ -8896,7 +8916,7 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C6">
         <v>2</v>
@@ -8912,7 +8932,7 @@
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C8">
         <v>3</v>
@@ -8923,7 +8943,7 @@
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C9">
         <v>3</v>
@@ -8934,7 +8954,7 @@
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C10">
         <v>3</v>
@@ -8945,7 +8965,7 @@
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C11">
         <v>2</v>
@@ -8953,7 +8973,7 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C12">
         <v>2</v>
@@ -8961,7 +8981,7 @@
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C13">
         <v>2</v>
@@ -8969,7 +8989,7 @@
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C14">
         <v>2</v>
@@ -8977,7 +8997,7 @@
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C15">
         <v>2</v>
@@ -8985,7 +9005,7 @@
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C16">
         <v>2</v>
@@ -8993,7 +9013,7 @@
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C17">
         <v>2</v>
@@ -9023,95 +9043,95 @@
   <sheetData>
     <row r="1" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C1" t="s">
         <v>257</v>
       </c>
       <c r="D1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="E1" t="s">
+        <v>443</v>
+      </c>
+      <c r="F1" t="s">
         <v>444</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>445</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>446</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
+        <v>449</v>
+      </c>
+      <c r="J1" t="s">
+        <v>450</v>
+      </c>
+      <c r="K1" t="s">
         <v>447</v>
       </c>
-      <c r="I1" t="s">
-        <v>450</v>
-      </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
+        <v>448</v>
+      </c>
+      <c r="M1" t="s">
         <v>451</v>
-      </c>
-      <c r="K1" t="s">
-        <v>448</v>
-      </c>
-      <c r="L1" t="s">
-        <v>449</v>
-      </c>
-      <c r="M1" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="F2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B3" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="F3" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="F4" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B5" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="F5" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B6" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
   </sheetData>
